--- a/仕様書/仕様.xlsx
+++ b/仕様書/仕様.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirit\source\repos\Wire-Action\仕様書\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5B156A-C479-4E60-863C-17E6F60ECDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-23055" yWindow="2430" windowWidth="19185" windowHeight="10065" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="タイトル画面" sheetId="1" r:id="rId1"/>
+    <sheet name="ステージ" sheetId="2" r:id="rId2"/>
+    <sheet name="memo " sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,14 +26,120 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>スプライトのアニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>system</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルの文字列画像</t>
+    <rPh sb="5" eb="10">
+      <t>モジレツガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景のアニメーションスプライトor画像</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CONTRINUE文字画像</t>
+    <rPh sb="9" eb="13">
+      <t>モジガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>QUIT文字列</t>
+    <rPh sb="4" eb="7">
+      <t>モジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データの読み込み</t>
+    <rPh sb="4" eb="5">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面に切り替え</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Entityにタグを持たせて管理側で検索したあぐのリストを作成して戻り値で返す</t>
+    <rPh sb="10" eb="11">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カンリガワ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +444,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:I7"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:9">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD00E591-9CE7-46F8-B377-92E8DE5E2B1F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC91E6D-E71D-4B76-8BFC-212EFE9B25AE}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>